--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1117 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:14</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/25</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/25</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1161,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/25</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,903 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/25</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC28"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:25</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/25</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1110,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:36</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1807,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,17 +1883,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1851,13 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -1885,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1918,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,17 +2002,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1962,13 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1996,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -2029,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2190,7 +2262,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2301,7 +2373,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2484,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2523,7 +2595,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2634,7 +2706,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2767,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2817,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2928,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2917,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3039,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3150,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3211,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3261,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3322,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3372,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3433,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3483,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/25</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3544,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3526,7 +3598,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/25</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3659,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3641,7 +3713,1264 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/25</t>
+          <t>13/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>12/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>10/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2179,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2212,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2236,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2434,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2545,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2656,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2767,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2878,7 +2886,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2989,7 +2997,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3322,7 +3330,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3552,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3659,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,7 +3782,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3885,7 +3893,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4008,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4115,7 +4123,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,7 +4238,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4353,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4460,7 +4468,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4575,7 +4583,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4686,7 +4694,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4801,7 +4809,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4863,22 +4871,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -4911,12 +4919,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4965,12 +4973,242 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>128.0</t>
         </is>
       </c>
-      <c r="AC39" s="2" t="inlineStr">
+      <c r="AC40" s="2" t="inlineStr">
         <is>
           <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>14/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC41"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2189,24 +2189,24 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2520,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2553,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2577,33 +2581,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2703,7 +2711,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2775,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,32 +2861,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2886,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2910,17 +2922,17 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
@@ -2930,13 +2942,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2997,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3075,32 +3091,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3108,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3132,17 +3152,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3152,13 +3172,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3330,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3441,7 +3465,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3576,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3606,7 +3630,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3691,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3721,7 +3745,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3806,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,7 +3917,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3947,7 +3971,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4032,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4062,7 +4086,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4147,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4177,7 +4201,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4262,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,7 +4377,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4407,7 +4431,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4492,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4522,7 +4546,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4607,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4694,7 +4718,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4748,7 +4772,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4833,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4863,7 +4887,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4948,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4978,7 +5002,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5063,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5093,7 +5117,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5101,22 +5125,22 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5149,12 +5173,12 @@
       <c r="M41" s="2" t="inlineStr"/>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5168,47 +5192,721 @@
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V41" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W41" s="2" t="inlineStr">
+      <c r="W42" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X41" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y41" s="2" t="inlineStr">
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z41" s="2" t="inlineStr">
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr">
-        <is>
-          <t>14/27</t>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>17/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>8/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,14 +3167,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>124.0</t>
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3321,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3354,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,17 +3382,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3398,13 +3402,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3504,7 +3512,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3543,32 +3551,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3576,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3600,37 +3612,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -3658,32 +3670,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3691,7 +3707,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3715,17 +3731,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3735,17 +3751,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -3773,32 +3789,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3806,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3830,33 +3850,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3884,32 +3908,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3917,7 +3945,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3941,17 +3969,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3961,7 +3989,7 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -3999,32 +4027,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4032,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4056,37 +4088,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4114,32 +4146,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4147,7 +4183,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4171,17 +4207,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4191,12 +4227,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4229,32 +4265,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4262,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4286,37 +4326,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -4344,32 +4384,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4377,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4401,37 +4445,37 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -4459,32 +4503,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4492,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4516,17 +4564,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4536,17 +4584,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -4574,12 +4622,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq39推进至seq50，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4607,7 +4655,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4615,10 +4663,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>沪南路高科西路</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±10分钟；反向位置物理seq39（站名待映射） ETA 4分钟参与校验</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4718,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4772,7 +4836,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4897,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,7 +5012,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5002,7 +5066,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5127,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5117,7 +5181,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5242,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5232,7 +5296,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5347,7 +5411,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5472,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5519,7 +5583,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5573,7 +5637,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5698,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5745,7 +5809,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5856,7 +5920,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5910,6 +5974,918 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>1/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>5/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>9/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>130.5</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>17/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3523,7 +3523,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4394,24 +4394,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4525,12 +4525,12 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq39推进至seq50，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq39推进至seq61，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4721,7 +4721,7 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4749,32 +4749,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -4782,7 +4786,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4806,29 +4810,29 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>129.0</t>
@@ -4836,7 +4840,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4951,7 +4955,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4979,32 +4983,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5012,7 +5020,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5036,17 +5044,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5056,17 +5064,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5094,32 +5102,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5127,7 +5139,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5151,17 +5163,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5171,17 +5183,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -5209,32 +5221,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5242,7 +5258,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5266,37 +5282,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>123.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5324,32 +5340,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5357,7 +5377,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5381,17 +5401,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5401,17 +5421,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5522,7 +5542,7 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5583,7 +5603,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5637,7 +5657,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5698,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5737,7 +5757,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5748,7 +5768,7 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5809,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5859,7 +5879,7 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5920,7 +5940,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5970,7 +5990,7 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6051,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6081,7 +6101,7 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6162,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6196,7 +6216,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6257,7 +6277,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6307,7 +6327,7 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6388,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6422,7 +6442,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6503,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6537,7 +6557,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6598,7 +6618,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6652,7 +6672,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6713,7 +6733,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6767,7 +6787,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6848,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6877,12 +6897,686 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,13 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,13 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2609,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2716,13 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2822,18 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3052,18 +3068,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3172,17 +3192,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,18 +3532,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3627,14 +3651,14 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3642,7 +3666,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3880,7 +3904,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,7 +4127,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4118,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4261,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4380,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4475,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4786,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5193,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5258,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5312,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5377,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5416,14 +5440,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>137.0</t>
@@ -5431,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5459,32 +5483,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5492,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5516,17 +5544,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5536,13 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5570,32 +5602,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5603,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5627,17 +5663,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5647,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -5685,32 +5721,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5718,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5742,17 +5782,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5762,13 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB45" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5796,32 +5840,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5829,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5853,33 +5901,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5907,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5940,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5964,17 +6020,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -5984,13 +6040,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB47" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6018,32 +6078,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -6051,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6075,33 +6139,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB48" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6129,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6162,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6186,17 +6258,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6206,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6244,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6277,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6301,33 +6377,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB50" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6355,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6388,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6412,29 +6496,29 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -6442,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6503,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6557,7 +6641,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6657,7 +6741,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6672,7 +6756,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6733,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6787,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6932,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6902,7 +6986,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6963,7 +7047,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7074,7 +7158,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7128,7 +7212,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -7189,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7300,7 +7384,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7354,7 +7438,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7415,7 +7499,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7526,7 +7610,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7570,13 +7654,707 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB61" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>24/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
     <col width="36" customWidth="1" min="20" max="20"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>139.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,14 +3770,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>139.0</t>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3894,17 +3894,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,17 +4132,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4370,12 +4370,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4484,14 +4484,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6326,24 +6326,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6402,12 +6402,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6445,24 +6445,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6554,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6587,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6611,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6631,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6669,32 +6673,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6702,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6726,17 +6734,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6746,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6784,32 +6792,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6817,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6841,17 +6853,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6861,12 +6873,12 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6899,32 +6911,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -6932,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6956,29 +6972,29 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -6986,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -7014,12 +7030,12 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7047,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7055,10 +7071,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q56" s="2" t="inlineStr"/>
-      <c r="R56" s="2" t="inlineStr"/>
-      <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 6分钟参与校验</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -7158,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7240,32 +7272,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7273,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7297,33 +7333,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7438,7 +7478,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7499,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7664,7 +7704,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7725,7 +7765,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7779,7 +7819,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7840,7 +7880,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7894,7 +7934,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7955,7 +7995,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8009,7 +8049,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8110,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8119,12 +8159,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8185,7 +8225,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8234,12 +8274,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8247,22 +8287,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8300,7 +8340,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8314,47 +8354,618 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>14:35</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>127.5</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>14/29</t>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>139.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>22/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5202,14 +5202,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6159,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq60，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7157,32 +7157,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7190,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7214,17 +7218,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7234,7 +7238,7 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
@@ -7282,24 +7286,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7309,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7358,12 +7362,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7478,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7506,32 +7510,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7539,7 +7547,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7563,33 +7571,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7617,32 +7629,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7650,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7674,17 +7690,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7694,17 +7710,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7732,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7765,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7789,17 +7809,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7809,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -7847,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7880,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7904,17 +7928,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7924,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7995,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8110,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8225,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8279,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8340,7 +8364,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8451,7 +8475,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8505,7 +8529,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8590,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8620,7 +8644,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -8681,7 +8705,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8735,7 +8759,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8796,7 +8820,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8858,22 +8882,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8906,12 +8930,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8925,47 +8949,733 @@
       <c r="T72" s="2" t="inlineStr"/>
       <c r="U72" s="2" t="inlineStr">
         <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
           <t>15:25</t>
         </is>
       </c>
-      <c r="V72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W72" s="2" t="inlineStr">
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X72" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y72" s="2" t="inlineStr">
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z72" s="2" t="inlineStr">
+      <c r="Z73" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>123.0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>1/29</t>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>23/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AC85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,14 +2604,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,13 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3378,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3493,7 +3497,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3537,12 +3541,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3612,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3656,17 +3660,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3785,7 +3789,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3889,7 +3893,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3969,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,14 +4012,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -4023,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4132,17 +4136,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -4207,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4261,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4326,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4365,14 +4369,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -4380,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4445,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4499,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4603,14 +4607,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>125.5</t>
@@ -4618,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4979,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,14 +5087,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>126.0</t>
@@ -5098,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5454,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,14 +5682,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -5693,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,12 +6168,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6273,7 +6277,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6353,7 +6357,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,12 +6401,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6472,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6520,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,7 +6634,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6710,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,17 +6758,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,14 +6872,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>127.0</t>
@@ -6883,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7547,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7758,24 +7762,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7785,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,12 +7838,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>27/29</t>
         </is>
       </c>
     </row>
@@ -7877,24 +7881,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7904,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7953,12 +7957,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7986,32 +7990,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8019,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,17 +8051,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8063,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8101,32 +8109,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8134,7 +8146,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,17 +8170,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8178,17 +8190,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8216,32 +8228,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8249,7 +8265,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,17 +8289,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8293,12 +8309,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8331,32 +8347,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8364,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,17 +8408,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8408,13 +8428,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8442,32 +8466,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8475,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8499,17 +8527,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8519,17 +8547,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/29</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8644,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>27/29</t>
+          <t>28/29</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8759,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8874,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9046,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9161,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9215,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9276,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9391,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9506,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9560,7 +9588,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -9621,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9679,6 +9707,811 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>4/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC85"/>
+  <dimension ref="A1:AC93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3774,17 +3774,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4250,22 +4250,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4493,17 +4493,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5325,7 +5325,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6996,17 +6996,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -8200,7 +8200,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>130.2</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>23/29</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -8585,32 +8585,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8618,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,32 +8646,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8700,32 +8704,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8733,7 +8741,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,17 +8765,17 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
@@ -8777,17 +8785,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8815,32 +8823,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8848,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,37 +8884,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8930,12 +8942,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -8963,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8971,10 +8983,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q72" s="2" t="inlineStr"/>
-      <c r="R72" s="2" t="inlineStr"/>
-      <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -9074,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9156,32 +9184,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9189,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9213,17 +9245,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9233,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9304,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9419,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9534,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9649,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9764,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9879,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9994,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10109,7 +10141,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10224,7 +10256,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10339,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10393,7 +10425,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10486,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10512,6 +10544,926 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>26/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>123.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>2/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>28/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC93"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,14 +2953,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3421,22 +3421,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4012,22 +4012,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7356,22 +7356,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9030,7 +9030,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9069,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9102,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,37 +9130,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9260,7 +9264,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9275,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9303,32 +9307,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9336,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,29 +9368,29 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -9390,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9418,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9451,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,37 +9487,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9533,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9566,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9590,17 +9606,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9610,12 +9626,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9648,32 +9664,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -9681,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,17 +9725,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9725,7 +9745,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9735,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9850,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -9878,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9911,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9935,37 +9959,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10026,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10141,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10256,7 +10280,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10310,7 +10334,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10371,7 +10395,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10425,7 +10449,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10510,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10540,7 +10564,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10625,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10655,7 +10679,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10831,7 +10855,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10946,7 +10970,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11061,7 +11085,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11176,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11291,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11345,7 +11369,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11406,7 +11430,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11460,7 +11484,923 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>123.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>27/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2375,17 +2375,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3187,22 +3187,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3893,22 +3893,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4265,7 +4265,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4374,17 +4374,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5568,17 +5568,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6277,22 +6277,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6634,22 +6634,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,17 +6877,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -7006,7 +7006,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7242,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8319,7 +8319,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>26/29</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9621,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10017,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10050,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10074,37 +10078,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10132,32 +10136,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10165,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,37 +10197,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -10247,32 +10255,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10280,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10304,37 +10316,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10362,32 +10374,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10395,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10419,17 +10435,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10439,17 +10455,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -10477,32 +10493,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10510,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10534,37 +10554,37 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10592,32 +10612,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10625,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10649,17 +10673,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10669,17 +10693,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -10707,32 +10731,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:25</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10740,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10764,17 +10792,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10784,17 +10812,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>26/29</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10937,32 +10965,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10970,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10994,17 +11026,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11014,17 +11046,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11085,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11200,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11315,7 +11347,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11430,7 +11462,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11484,7 +11516,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -11545,7 +11577,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11660,7 +11692,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11771,7 +11803,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11886,7 +11918,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12001,7 +12033,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12116,7 +12148,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12231,7 +12263,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12293,22 +12325,22 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -12341,12 +12373,12 @@
       <c r="M101" s="2" t="inlineStr"/>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12360,47 +12392,737 @@
       <c r="T101" s="2" t="inlineStr"/>
       <c r="U101" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>3/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V101" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W101" s="2" t="inlineStr">
+      <c r="W102" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X101" s="2" t="inlineStr">
+      <c r="X102" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y101" s="2" t="inlineStr">
+      <c r="Y102" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z101" s="2" t="inlineStr">
+      <c r="Z102" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA101" s="2" t="inlineStr">
+      <c r="AA102" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB101" s="2" t="inlineStr">
+      <c r="AB102" s="2" t="inlineStr">
         <is>
           <t>129.3</t>
         </is>
       </c>
-      <c r="AC101" s="2" t="inlineStr">
+      <c r="AC102" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>130.3</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>125.3</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>126.3</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>8/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr"/>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr"/>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q107" s="2" t="inlineStr"/>
+      <c r="R107" s="2" t="inlineStr"/>
+      <c r="S107" s="2" t="inlineStr"/>
+      <c r="T107" s="2" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>125.7</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC107"/>
+  <dimension ref="A1:AC111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,17 +2719,17 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3029,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3073,17 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3426,17 +3426,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6039,17 +6039,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,17 +6163,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7952,17 +7952,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9507,17 +9507,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -10850,32 +10850,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10883,7 +10887,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10907,17 +10911,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10927,12 +10931,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>123.5</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10987,12 +10991,12 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11002,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11041,7 +11045,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11117,7 +11121,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11232,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11314,32 +11318,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11347,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11371,17 +11379,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11391,17 +11399,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11462,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11577,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11631,7 +11639,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -11659,12 +11667,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq56，推进18站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11692,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,10 +11708,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="2" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 20分钟参与校验</t>
+        </is>
+      </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11770,32 +11794,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11803,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11827,32 +11855,32 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11885,32 +11913,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11918,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11942,17 +11974,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11962,17 +11994,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12033,7 +12065,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12115,32 +12147,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12148,7 +12184,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12172,17 +12208,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12192,17 +12228,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12263,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12317,7 +12353,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12378,7 +12414,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12493,7 +12529,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12608,7 +12644,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12723,7 +12759,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12838,7 +12874,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12892,7 +12928,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12953,7 +12989,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13015,22 +13051,22 @@
       <c r="A107" s="2" t="inlineStr"/>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -13063,12 +13099,12 @@
       <c r="M107" s="2" t="inlineStr"/>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13082,47 +13118,507 @@
       <c r="T107" s="2" t="inlineStr"/>
       <c r="U107" s="2" t="inlineStr">
         <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W107" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z107" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB107" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC107" s="2" t="inlineStr">
+        <is>
+          <t>17/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr"/>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr"/>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr"/>
+      <c r="R108" s="2" t="inlineStr"/>
+      <c r="S108" s="2" t="inlineStr"/>
+      <c r="T108" s="2" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
           <t>20:05</t>
         </is>
       </c>
-      <c r="V107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q109" s="2" t="inlineStr"/>
+      <c r="R109" s="2" t="inlineStr"/>
+      <c r="S109" s="2" t="inlineStr"/>
+      <c r="T109" s="2" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V109" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="W109" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X107" s="2" t="inlineStr">
+      <c r="X109" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y107" s="2" t="inlineStr">
+      <c r="Y109" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z107" s="2" t="inlineStr">
+      <c r="Z109" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA107" s="2" t="inlineStr">
+      <c r="AA109" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB107" s="2" t="inlineStr">
+      <c r="AB109" s="2" t="inlineStr">
         <is>
           <t>125.7</t>
         </is>
       </c>
-      <c r="AC107" s="2" t="inlineStr">
+      <c r="AC109" s="2" t="inlineStr">
         <is>
           <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr"/>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="2" t="inlineStr"/>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q110" s="2" t="inlineStr"/>
+      <c r="R110" s="2" t="inlineStr"/>
+      <c r="S110" s="2" t="inlineStr"/>
+      <c r="T110" s="2" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X110" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y110" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z110" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA110" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB110" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC110" s="2" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr"/>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr"/>
+      <c r="K111" s="2" t="inlineStr"/>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr"/>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q111" s="2" t="inlineStr"/>
+      <c r="R111" s="2" t="inlineStr"/>
+      <c r="S111" s="2" t="inlineStr"/>
+      <c r="T111" s="2" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W111" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X111" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y111" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z111" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA111" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB111" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC111" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,17 +4973,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6238,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,17 +9269,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9512,12 +9512,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -9582,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,12 +9860,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11409,7 +11409,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11923,24 +11923,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11999,12 +11999,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>127.7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12032,32 +12032,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -12065,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12089,17 +12093,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12109,12 +12113,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12157,24 +12161,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12184,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12233,12 +12237,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>128.3</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12266,32 +12270,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12299,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12323,17 +12331,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12343,17 +12351,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -12381,12 +12389,12 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq60，推进32站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -12414,7 +12422,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12422,10 +12430,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
       <c r="R101" s="2" t="inlineStr"/>
       <c r="S101" s="2" t="inlineStr"/>
-      <c r="T101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq25映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U101" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -12496,32 +12512,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12529,7 +12549,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12553,17 +12573,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12573,12 +12593,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12611,32 +12631,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -12644,7 +12668,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12668,17 +12692,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12688,12 +12712,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12726,12 +12750,12 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12759,7 +12783,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12767,10 +12791,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q104" s="2" t="inlineStr"/>
-      <c r="R104" s="2" t="inlineStr"/>
-      <c r="S104" s="2" t="inlineStr"/>
-      <c r="T104" s="2" t="inlineStr"/>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>白桦路明月路</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr">
+        <is>
+          <t>20:18</t>
+        </is>
+      </c>
+      <c r="S104" s="2" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="T104" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq25映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U104" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12874,7 +12914,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12928,7 +12968,7 @@
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12989,7 +13029,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13071,32 +13111,36 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J107" s="2" t="inlineStr"/>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M107" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -13104,7 +13148,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13128,17 +13172,17 @@
       </c>
       <c r="W107" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X107" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y107" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z107" s="2" t="inlineStr">
@@ -13148,12 +13192,12 @@
       </c>
       <c r="AA107" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB107" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC107" s="2" t="inlineStr">
@@ -13219,7 +13263,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13334,7 +13378,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13449,7 +13493,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13564,7 +13608,7 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">

--- a/data/export/2026-10-02-浦东35路.xlsx
+++ b/data/export/2026-10-02-浦东35路.xlsx
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5092,17 +5092,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5925,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6292,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10336,17 +10336,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10530,7 +10530,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -10941,7 +10941,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -11006,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12361,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12484,7 +12484,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12755,7 +12755,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq55，推进27站，达到≥2站确认条件</t>
+          <t>原方向在全程38%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12853,7 +12853,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -12996,32 +12996,36 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr"/>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M106" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -13029,7 +13033,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13053,17 +13057,17 @@
       </c>
       <c r="W106" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X106" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y106" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z106" s="2" t="inlineStr">
@@ -13073,17 +13077,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>126.3</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13148,7 +13152,7 @@
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P107" s="2" t="inlineStr">
@@ -13230,32 +13234,36 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:54</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N108" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -13263,7 +13271,7 @@
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P108" s="2" t="inlineStr">
@@ -13287,17 +13295,17 @@
       </c>
       <c r="W108" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X108" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y108" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z108" s="2" t="inlineStr">
@@ -13307,17 +13315,17 @@
       </c>
       <c r="AA108" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>122.7</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -13345,32 +13353,36 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -13378,7 +13390,7 @@
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P109" s="2" t="inlineStr">
@@ -13402,17 +13414,17 @@
       </c>
       <c r="W109" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X109" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y109" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z109" s="2" t="inlineStr">
@@ -13422,17 +13434,17 @@
       </c>
       <c r="AA109" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB109" s="2" t="inlineStr">
         <is>
-          <t>125.7</t>
+          <t>125.2</t>
         </is>
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13493,7 +13505,7 @@
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P110" s="2" t="inlineStr">
@@ -13547,7 +13559,7 @@
       </c>
       <c r="AC110" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13620,7 @@
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="P111" s="2" t="inlineStr">
